--- a/growth-os/dist/Founderz_Growth_OS.xlsx
+++ b/growth-os/dist/Founderz_Growth_OS.xlsx
@@ -1146,14 +1146,14 @@
     <row r="8" ht="30" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3. Le dices al agente «sincroniza el Growth OS». El agente lee el Excel, actualiza los YAML del repo y hace commit: ahí queda el histórico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+          <t>3. Le dices al agente «sincroniza el Growth OS». El agente lee el Excel desde OneDrive, actualiza los YAML del repo y hace commit: ahí queda el histórico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>4. Cuando hay cambios estructurales (nuevos departamentos, columnas, métricas o reglas de cálculo), el agente regenera el Excel y lo vuelve a subir.</t>
+          <t>4. Cuando hay cambios estructurales (nuevos departamentos, columnas, métricas o reglas de cálculo), el agente regenera el fichero y te lo entrega para que lo dejes en la carpeta. Sustituye el anterior y sigues trabajando.</t>
         </is>
       </c>
     </row>
